--- a/data/trans_orig/IQ23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de horas que duerme</t>
+          <t>Menores según del número de horas que duerme (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 11,98</t>
+          <t>11,29; 11,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,3; 11,96</t>
+          <t>11,27; 11,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 11,64</t>
+          <t>11,08; 11,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 10,61</t>
+          <t>9,96; 10,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 11,91</t>
+          <t>11,24; 11,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 12,25</t>
+          <t>11,49; 12,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 11,62</t>
+          <t>10,94; 11,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 10,86</t>
+          <t>10,15; 10,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 11,83</t>
+          <t>11,36; 11,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 12,01</t>
+          <t>11,5; 11,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 11,53</t>
+          <t>11,1; 11,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 10,62</t>
+          <t>10,13; 10,61</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,83</t>
+          <t>9,62; 9,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 9,89</t>
+          <t>9,66; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,42 +871,42 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,53</t>
+          <t>9,27; 9,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,92</t>
+          <t>9,72; 9,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,79</t>
+          <t>9,58; 9,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,57</t>
+          <t>9,36; 9,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,49</t>
+          <t>9,23; 9,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,84</t>
+          <t>9,7; 9,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 9,81</t>
+          <t>9,64; 9,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,62</t>
+          <t>9,45; 9,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,35</t>
+          <t>9,1; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 9,37</t>
+          <t>9,11; 9,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,19</t>
+          <t>8,96; 9,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,13</t>
+          <t>8,91; 9,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,22</t>
+          <t>8,99; 9,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 9,02</t>
+          <t>8,8; 9,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,36</t>
+          <t>9,16; 9,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1141,52 +1141,52 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>8,66; 8,87</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>8,65; 8,88</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,65; 8,88</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 8,89</t>
+          <t>8,68; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 8,82</t>
+          <t>8,62; 8,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 8,94</t>
+          <t>8,71; 8,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 8,86</t>
+          <t>8,64; 8,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 8,9</t>
+          <t>8,62; 8,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 8,76</t>
+          <t>8,61; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 8,87</t>
+          <t>8,72; 8,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 8,84</t>
+          <t>8,68; 8,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,71</t>
+          <t>9,53; 9,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,91</t>
+          <t>9,68; 9,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 9,21</t>
+          <t>9,06; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,73</t>
+          <t>9,55; 9,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,93</t>
+          <t>9,71; 9,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,6</t>
+          <t>9,41; 9,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,16</t>
+          <t>8,99; 9,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,7</t>
+          <t>9,56; 9,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,88</t>
+          <t>9,73; 9,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,62</t>
+          <t>9,49; 9,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,05; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Edad-trans_orig.xlsx
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 11,99</t>
+          <t>11,31; 12,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 11,97</t>
+          <t>11,27; 11,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 11,7</t>
+          <t>11,06; 11,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 10,63</t>
+          <t>9,97; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 11,9</t>
+          <t>11,28; 11,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 11,6</t>
+          <t>10,95; 11,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 10,81</t>
+          <t>10,11; 10,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 11,85</t>
+          <t>11,39; 11,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 11,97</t>
+          <t>11,5; 12,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 11,56</t>
+          <t>11,1; 11,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 10,61</t>
+          <t>10,15; 10,64</t>
         </is>
       </c>
     </row>
@@ -856,32 +856,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,81</t>
+          <t>9,62; 9,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 9,9</t>
+          <t>9,65; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,75</t>
+          <t>9,51; 9,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,54</t>
+          <t>9,3; 9,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,93</t>
+          <t>9,71; 9,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 9,8</t>
+          <t>9,57; 9,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,47</t>
+          <t>9,24; 9,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,84</t>
+          <t>9,69; 9,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 9,8</t>
+          <t>9,65; 9,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,61</t>
+          <t>9,46; 9,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,47</t>
+          <t>9,3; 9,47</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,36</t>
+          <t>9,11; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,34</t>
+          <t>9,12; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,24</t>
+          <t>9,02; 9,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,2</t>
+          <t>8,95; 9,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,13</t>
+          <t>8,92; 9,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 9,46</t>
+          <t>9,13; 9,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,22</t>
+          <t>9,0; 9,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 9,04</t>
+          <t>8,79; 9,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>9,03; 9,2</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9,16; 9,35</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>9,04; 9,2</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 9,35</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,2</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,07</t>
+          <t>8,91; 9,08</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 8,76</t>
+          <t>8,57; 8,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 8,87</t>
+          <t>8,66; 8,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 8,89</t>
+          <t>8,67; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 8,93</t>
+          <t>8,72; 8,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 8,91</t>
+          <t>8,6; 8,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 8,75</t>
+          <t>8,62; 8,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 8,88</t>
+          <t>8,71; 8,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 8,84</t>
+          <t>8,68; 8,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 9,9</t>
+          <t>9,7; 9,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,37 +1291,37 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,21</t>
+          <t>9,07; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,74</t>
+          <t>9,55; 9,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,92</t>
+          <t>9,71; 9,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,61</t>
+          <t>9,42; 9,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,15</t>
+          <t>9,0; 9,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,7</t>
+          <t>9,57; 9,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,88</t>
+          <t>9,73; 9,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,05; 9,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,52</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,36</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,57</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,84</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>10,35</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,31; 12,03</t>
+          <t>11,24; 11,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 11,96</t>
+          <t>11,5; 12,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 11,68</t>
+          <t>10,95; 11,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 10,61</t>
+          <t>10,21; 10,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 11,9</t>
+          <t>11,27; 11,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 12,23</t>
+          <t>11,3; 11,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 11,57</t>
+          <t>11,06; 11,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 10,82</t>
+          <t>9,91; 10,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 11,83</t>
+          <t>11,35; 11,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 12,01</t>
+          <t>11,49; 12,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 11,54</t>
+          <t>11,06; 11,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 10,64</t>
+          <t>10,13; 10,64</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,68</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,46</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,36</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,63</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9,41</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9,71; 9,92</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9,57; 9,79</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9,34; 9,57</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9,23; 9,49</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9,62; 9,83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,65; 9,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,75</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,3; 9,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,92</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,8</t>
+          <t>9,65; 9,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,58</t>
+          <t>9,52; 9,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,5</t>
+          <t>9,29; 9,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 9,81</t>
+          <t>9,64; 9,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,61</t>
+          <t>9,46; 9,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,47</t>
+          <t>9,29; 9,47</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,91</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,27</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,92</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,36</t>
+          <t>8,92; 9,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 9,35</t>
+          <t>9,14; 9,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 9,23</t>
+          <t>9,0; 9,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,21</t>
+          <t>8,81; 9,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,14</t>
+          <t>9,1; 9,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 9,45</t>
+          <t>9,12; 9,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,23</t>
+          <t>9,03; 9,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 9,02</t>
+          <t>8,96; 9,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,2</t>
+          <t>9,04; 9,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,35</t>
+          <t>9,16; 9,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,08</t>
+          <t>8,91; 9,07</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,82</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,75</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,74</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,77</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,77</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,71</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,82</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,75</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>8,73</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 8,74</t>
+          <t>8,61; 8,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 8,88</t>
+          <t>8,72; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>8,64; 8,86</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8,62; 8,88</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,56; 8,76</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>8,65; 8,88</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,67; 8,89</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8,62; 8,83</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,72; 8,93</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 8,87</t>
+          <t>8,65; 8,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 8,89</t>
+          <t>8,63; 8,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 8,87</t>
+          <t>8,72; 8,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 8,83</t>
+          <t>8,69; 8,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 8,86</t>
+          <t>8,64; 8,82</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9,8</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,72</t>
+          <t>9,54; 9,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,91</t>
+          <t>9,72; 9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>9,42; 9,6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8,99; 9,14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,52; 9,71</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,91</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 9,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,94</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,16</t>
+          <t>9,04; 9,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,89</t>
+          <t>9,72; 9,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,62</t>
+          <t>9,48; 9,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,03; 9,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,57</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,84</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,63</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,62</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,36</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11,6</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11,73</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,35</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>11.57147437386023</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11.83616063165918</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11.25429388816075</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.51835269961851</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>11.62501960883136</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>11.61893638229385</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>11.36029306022266</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>10.1944808325561</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>11.59656045768022</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>11.72701345400695</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>11.30849510372554</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>10.35452754998464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11,24; 11,91</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11,5; 12,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10,95; 11,62</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,21; 10,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11,27; 11,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,3; 11,96</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,06; 11,64</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9,91; 10,55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11,35; 11,83</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11,49; 12,01</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11,06; 11,53</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,13; 10,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>11.24230558784719</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>11.49728838012288</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.95187980526733</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10.21291366934493</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>11.27307188278158</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>11.30243169021541</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.06089073076498</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>9.90670706980225</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>11.34913736119847</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>11.49414149100182</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>11.06431483268088</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>10.12588316335136</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.90832280973023</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.2511437413714</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.61593120765335</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.96327203957459</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.98072990985322</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>11.96073530018636</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>11.64474244341764</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10.55064662923929</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>11.83271540129885</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>12.00708441143342</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>11.53031152245779</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>10.63887422741985</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,72</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,92</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 9,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 9,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,23; 9,49</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 9,83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,65; 9,89</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,75</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,29; 9,54</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,84</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 9,81</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,62</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,29; 9,47</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>9.81530216045936</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>9.684425137406212</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.462033648226468</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.355346640326925</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>9.720029705544562</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>9.772966520692005</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9.629369309482668</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9.410495175698266</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9.767790691883487</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>9.725753461926168</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>9.536856685525878</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.381828652690807</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,23</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,13</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,09</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,99</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9.709048803041789</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>9.573741073419022</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>9.343602069783925</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.230803163761172</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>9.619803847788161</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>9.651960779846732</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>9.515795859009597</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>9.291660816621881</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9.693195711736902</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>9.643642925991891</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>9.461789642526375</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.288768518935495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8,92; 9,13</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,14; 9,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,0; 9,22</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8,81; 9,01</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,1; 9,35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,12; 9,37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,24</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,96; 9,2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,2</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 9,36</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,2</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,91; 9,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.923213395047009</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.791739202883956</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.569562305515317</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.489993309928767</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>9.828956794740314</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>9.887845708783084</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>9.745019295564697</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.535524720708372</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>9.836939067900662</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>9.813279628033291</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9.62161016083914</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.466269261452712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,75</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,74</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,65</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8,72</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8,79</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8,76</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>9.02471727797605</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.272527698601637</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.108882920276253</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.912149734342211</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.218223631744889</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>9.232718849935102</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>9.130800895622796</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.086410751734642</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.115678570769209</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>9.252762511306623</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>9.119905298406891</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>8.993712418464805</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 8,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,72; 8,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,64; 8,86</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,62; 8,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8,56; 8,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,65; 8,88</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,65; 8,88</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,63; 8,82</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8,62; 8,76</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8,72; 8,87</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8,69; 8,84</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,64; 8,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>8.922205761751659</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.139047066157964</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8.999941702232258</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8.809729900710998</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>9.099241427881049</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9.11813185441742</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>9.029063829156058</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>8.964044731250988</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>9.042586297023719</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>9.158182037312548</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>9.040792036066199</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>8.914150781197135</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.134879181516938</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.463957213501928</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.216105483979536</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.012021879881797</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.354154192303875</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.369353388092367</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9.243612023408925</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.197915899455893</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.198852282189902</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>9.356156737178674</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>9.196621240601338</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.074632968955481</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8.709769460359828</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.822653101143075</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8.752670852388055</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>8.744355142703968</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>8.653659361197915</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>8.765362148601605</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>8.765618640110072</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>8.721772909245631</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>8.682620109024645</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>8.794657133016287</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>8.759188641648466</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>8.73391268689817</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>8.606831107827279</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>8.718031092069332</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.635392517549748</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8.619212449366044</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8.556229186756962</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>8.64586385376372</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>8.648586277175074</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>8.627237266950997</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8.619630108594968</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>8.723398527038626</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>8.686624948658594</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>8.640376391183407</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.822484323965879</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.937803113275315</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.859116655736674</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.877692214441014</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.758231748619913</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>8.882729241827748</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>8.879181998549001</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>8.821243375374294</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8.761464058527</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>8.871031880243539</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>8.836067704121218</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>8.81888121857372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 9,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8,99; 9,14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 9,7</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,88</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>9.637760359470542</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>9.80790121623571</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>9.509073108734622</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.057991276864716</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>9.621690256596413</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>9.792403738930492</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>9.601496861439047</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>9.106919397633346</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>9.629980759722818</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>9.800376348193176</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>9.554031594785314</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.081057911973323</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>9.539005799528955</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>9.715272555308113</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>9.42374014686669</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>8.988139821054755</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>9.524544694177933</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9.691229195408974</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>9.513760991168251</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>9.044342265019466</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>9.566484641687268</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>9.722331055547787</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>9.484997006472435</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.029326328152754</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.73478873276642</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.934052406974539</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.603750309980549</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.143586783943322</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>9.711627205958811</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>9.907885398717834</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>9.698176989022093</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.181730494999783</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>9.698434500607341</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>9.884015437776576</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>9.622101629564806</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.131647260777667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
